--- a/12618117.xlsx
+++ b/12618117.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Krish\Desktop\MCA_SEM1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27CA99BE-B98F-4165-BD0C-343AF0AA35E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACD4243F-853C-443D-B72C-37EB129C4046}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="77">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -263,6 +263,9 @@
   </si>
   <si>
     <t>I had cold, cough and sore throat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Was a regular day </t>
   </si>
 </sst>
 </file>
@@ -2173,7 +2176,9 @@
       </c>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A30" s="13"/>
+      <c r="A30" s="8">
+        <v>46270</v>
+      </c>
       <c r="B30" s="14"/>
       <c r="C30" s="14"/>
       <c r="D30" s="14"/>
@@ -2196,7 +2201,9 @@
       <c r="O30" s="17"/>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A31" s="13"/>
+      <c r="A31" s="8">
+        <v>46271</v>
+      </c>
       <c r="B31" s="14"/>
       <c r="C31" s="14"/>
       <c r="D31" s="14"/>
@@ -2219,7 +2226,9 @@
       <c r="O31" s="17"/>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A32" s="13"/>
+      <c r="A32" s="8">
+        <v>46272</v>
+      </c>
       <c r="B32" s="14"/>
       <c r="C32" s="14"/>
       <c r="D32" s="14"/>
@@ -2242,50 +2251,100 @@
       <c r="O32" s="17"/>
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A33" s="13"/>
-      <c r="B33" s="14"/>
-      <c r="C33" s="14"/>
-      <c r="D33" s="14"/>
-      <c r="E33" s="14"/>
-      <c r="F33" s="14"/>
-      <c r="G33" s="14"/>
-      <c r="H33" s="14"/>
-      <c r="I33" s="15" t="str">
+      <c r="A33" s="8">
+        <v>46273</v>
+      </c>
+      <c r="B33" s="14">
+        <v>300</v>
+      </c>
+      <c r="C33" s="14">
+        <v>30</v>
+      </c>
+      <c r="D33" s="14">
+        <v>0</v>
+      </c>
+      <c r="E33" s="14">
+        <v>30</v>
+      </c>
+      <c r="F33" s="14">
+        <v>250</v>
+      </c>
+      <c r="G33" s="14">
+        <v>5</v>
+      </c>
+      <c r="H33" s="14">
+        <v>350</v>
+      </c>
+      <c r="I33" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J33" s="15" t="str">
+        <v>960</v>
+      </c>
+      <c r="J33" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K33" s="16"/>
-      <c r="L33" s="16"/>
-      <c r="M33" s="16"/>
+        <v>480</v>
+      </c>
+      <c r="K33" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="L33" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="M33" s="16" t="s">
+        <v>49</v>
+      </c>
       <c r="N33" s="17"/>
-      <c r="O33" s="17"/>
+      <c r="O33" s="17">
+        <v>4035</v>
+      </c>
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A34" s="13"/>
-      <c r="B34" s="14"/>
-      <c r="C34" s="14"/>
-      <c r="D34" s="14"/>
-      <c r="E34" s="14"/>
-      <c r="F34" s="14"/>
-      <c r="G34" s="14"/>
-      <c r="H34" s="14"/>
-      <c r="I34" s="15" t="str">
+      <c r="A34" s="8">
+        <v>46274</v>
+      </c>
+      <c r="B34" s="14">
+        <v>300</v>
+      </c>
+      <c r="C34" s="14">
+        <v>30</v>
+      </c>
+      <c r="D34" s="14">
+        <v>40</v>
+      </c>
+      <c r="E34" s="14">
+        <v>0</v>
+      </c>
+      <c r="F34" s="14">
+        <v>250</v>
+      </c>
+      <c r="G34" s="14">
+        <v>5</v>
+      </c>
+      <c r="H34" s="14">
+        <v>300</v>
+      </c>
+      <c r="I34" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J34" s="15" t="str">
+        <v>920</v>
+      </c>
+      <c r="J34" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K34" s="16"/>
-      <c r="L34" s="16"/>
-      <c r="M34" s="16"/>
-      <c r="N34" s="17"/>
-      <c r="O34" s="17"/>
+        <v>520</v>
+      </c>
+      <c r="K34" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="L34" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="M34" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="N34" s="17" t="s">
+        <v>76</v>
+      </c>
+      <c r="O34" s="17">
+        <v>8053</v>
+      </c>
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A35" s="13"/>

--- a/12618117.xlsx
+++ b/12618117.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Krish\Desktop\MCA_SEM1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACD4243F-853C-443D-B72C-37EB129C4046}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7154361-327D-496F-A501-0D9F5226A335}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="77">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2198,7 +2198,9 @@
       <c r="L30" s="16"/>
       <c r="M30" s="16"/>
       <c r="N30" s="17"/>
-      <c r="O30" s="17"/>
+      <c r="O30" s="17">
+        <v>284</v>
+      </c>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A31" s="8">
@@ -2223,7 +2225,9 @@
       <c r="L31" s="16"/>
       <c r="M31" s="16"/>
       <c r="N31" s="17"/>
-      <c r="O31" s="17"/>
+      <c r="O31" s="17">
+        <v>815</v>
+      </c>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A32" s="8">
@@ -2248,7 +2252,9 @@
       <c r="L32" s="16"/>
       <c r="M32" s="16"/>
       <c r="N32" s="17"/>
-      <c r="O32" s="17"/>
+      <c r="O32" s="17">
+        <v>10166</v>
+      </c>
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A33" s="8">
@@ -2347,27 +2353,51 @@
       </c>
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A35" s="13"/>
-      <c r="B35" s="14"/>
-      <c r="C35" s="14"/>
-      <c r="D35" s="14"/>
-      <c r="E35" s="14"/>
-      <c r="F35" s="14"/>
-      <c r="G35" s="14"/>
-      <c r="H35" s="14"/>
-      <c r="I35" s="15" t="str">
+      <c r="A35" s="8">
+        <v>46275</v>
+      </c>
+      <c r="B35" s="14">
+        <v>200</v>
+      </c>
+      <c r="C35" s="14">
+        <v>30</v>
+      </c>
+      <c r="D35" s="14">
+        <v>30</v>
+      </c>
+      <c r="E35" s="14">
+        <v>30</v>
+      </c>
+      <c r="F35" s="14">
+        <v>100</v>
+      </c>
+      <c r="G35" s="14">
+        <v>2</v>
+      </c>
+      <c r="H35" s="14">
+        <v>350</v>
+      </c>
+      <c r="I35" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J35" s="15" t="str">
+        <v>740</v>
+      </c>
+      <c r="J35" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K35" s="16"/>
-      <c r="L35" s="16"/>
-      <c r="M35" s="16"/>
+        <v>700</v>
+      </c>
+      <c r="K35" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="L35" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="M35" s="16" t="s">
+        <v>49</v>
+      </c>
       <c r="N35" s="17"/>
-      <c r="O35" s="17"/>
+      <c r="O35" s="17">
+        <v>5919</v>
+      </c>
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A36" s="13"/>

--- a/12618117.xlsx
+++ b/12618117.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Krish\Desktop\MCA_SEM1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7154361-327D-496F-A501-0D9F5226A335}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F078E98D-7575-43C0-BE0B-CE3C11594249}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="78">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -266,6 +266,9 @@
   </si>
   <si>
     <t xml:space="preserve">Was a regular day </t>
+  </si>
+  <si>
+    <t>Worked on project ResumeOS</t>
   </si>
 </sst>
 </file>
@@ -2400,27 +2403,53 @@
       </c>
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A36" s="13"/>
-      <c r="B36" s="14"/>
-      <c r="C36" s="14"/>
-      <c r="D36" s="14"/>
-      <c r="E36" s="14"/>
-      <c r="F36" s="14"/>
-      <c r="G36" s="14"/>
-      <c r="H36" s="14"/>
-      <c r="I36" s="15" t="str">
+      <c r="A36" s="8">
+        <v>46276</v>
+      </c>
+      <c r="B36" s="14">
+        <v>220</v>
+      </c>
+      <c r="C36" s="14">
+        <v>40</v>
+      </c>
+      <c r="D36" s="14">
+        <v>30</v>
+      </c>
+      <c r="E36" s="14">
+        <v>120</v>
+      </c>
+      <c r="F36" s="14">
+        <v>250</v>
+      </c>
+      <c r="G36" s="14">
+        <v>5</v>
+      </c>
+      <c r="H36" s="14">
+        <v>400</v>
+      </c>
+      <c r="I36" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J36" s="15" t="str">
+        <v>1060</v>
+      </c>
+      <c r="J36" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K36" s="16"/>
-      <c r="L36" s="16"/>
-      <c r="M36" s="16"/>
-      <c r="N36" s="17"/>
-      <c r="O36" s="17"/>
+        <v>380</v>
+      </c>
+      <c r="K36" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L36" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M36" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="N36" s="17" t="s">
+        <v>77</v>
+      </c>
+      <c r="O36" s="17">
+        <v>9271</v>
+      </c>
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A37" s="13"/>

--- a/12618117.xlsx
+++ b/12618117.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Krish\Desktop\MCA_SEM1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F078E98D-7575-43C0-BE0B-CE3C11594249}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F62067A-D381-4A64-8EA4-968F87CA4BA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="78">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -193,9 +193,6 @@
     <t>Kripal Singh</t>
   </si>
   <si>
-    <t>August</t>
-  </si>
-  <si>
     <t>D1P2635</t>
   </si>
   <si>
@@ -269,6 +266,9 @@
   </si>
   <si>
     <t>Worked on project ResumeOS</t>
+  </si>
+  <si>
+    <t>August, September</t>
   </si>
 </sst>
 </file>
@@ -977,7 +977,7 @@
         <v>32</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C3" s="21"/>
       <c r="D3" s="21"/>
@@ -985,7 +985,7 @@
         <v>33</v>
       </c>
       <c r="F3" s="21" t="s">
-        <v>52</v>
+        <v>77</v>
       </c>
       <c r="G3" s="21"/>
     </row>
@@ -1051,7 +1051,7 @@
         <v>48</v>
       </c>
       <c r="O5" s="7" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.35">
@@ -1088,16 +1088,16 @@
         <v>280</v>
       </c>
       <c r="K6" s="11" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="L6" s="11" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="M6" s="11" t="s">
         <v>49</v>
       </c>
       <c r="N6" s="12" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O6" s="18">
         <v>9900</v>
@@ -1137,16 +1137,16 @@
         <v>280</v>
       </c>
       <c r="K7" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="L7" s="16" t="s">
         <v>56</v>
-      </c>
-      <c r="L7" s="16" t="s">
-        <v>57</v>
       </c>
       <c r="M7" s="16" t="s">
         <v>49</v>
       </c>
       <c r="N7" s="17" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="O7" s="17">
         <v>8023</v>
@@ -1186,16 +1186,16 @@
         <v>390</v>
       </c>
       <c r="K8" s="16" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="L8" s="16" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="M8" s="16" t="s">
         <v>49</v>
       </c>
       <c r="N8" s="17" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="O8" s="17">
         <v>11206</v>
@@ -1235,16 +1235,16 @@
         <v>550</v>
       </c>
       <c r="K9" s="16" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="L9" s="16" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="M9" s="16" t="s">
         <v>49</v>
       </c>
       <c r="N9" s="17" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="O9" s="17">
         <v>633</v>
@@ -1284,16 +1284,16 @@
         <v>660</v>
       </c>
       <c r="K10" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="L10" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="M10" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="N10" s="17" t="s">
         <v>63</v>
-      </c>
-      <c r="L10" s="16" t="s">
-        <v>61</v>
-      </c>
-      <c r="M10" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="N10" s="17" t="s">
-        <v>64</v>
       </c>
       <c r="O10" s="17">
         <v>590</v>
@@ -1333,16 +1333,16 @@
         <v>550</v>
       </c>
       <c r="K11" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="L11" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="M11" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="N11" s="17" t="s">
         <v>63</v>
-      </c>
-      <c r="L11" s="16" t="s">
-        <v>65</v>
-      </c>
-      <c r="M11" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="N11" s="17" t="s">
-        <v>64</v>
       </c>
       <c r="O11" s="17">
         <v>5399</v>
@@ -1382,16 +1382,16 @@
         <v>360</v>
       </c>
       <c r="K12" s="16" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="L12" s="16" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="M12" s="16" t="s">
         <v>49</v>
       </c>
       <c r="N12" s="17" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="O12" s="17">
         <v>10744</v>
@@ -1431,16 +1431,16 @@
         <v>340</v>
       </c>
       <c r="K13" s="16" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="L13" s="16" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="M13" s="16" t="s">
         <v>49</v>
       </c>
       <c r="N13" s="17" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="O13" s="17">
         <v>12903</v>
@@ -1480,16 +1480,16 @@
         <v>270</v>
       </c>
       <c r="K14" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="L14" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="L14" s="16" t="s">
-        <v>57</v>
-      </c>
       <c r="M14" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="N14" s="17" t="s">
         <v>69</v>
-      </c>
-      <c r="N14" s="17" t="s">
-        <v>70</v>
       </c>
       <c r="O14" s="17">
         <v>12016</v>
@@ -1529,13 +1529,13 @@
         <v>390</v>
       </c>
       <c r="K15" s="16" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="L15" s="16" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="M15" s="16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="N15" s="17"/>
       <c r="O15" s="17">
@@ -1576,10 +1576,10 @@
         <v>685</v>
       </c>
       <c r="K16" s="16" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="L16" s="16" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="M16" s="16" t="s">
         <v>49</v>
@@ -1623,10 +1623,10 @@
         <v>610</v>
       </c>
       <c r="K17" s="16" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="L17" s="16" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="M17" s="16" t="s">
         <v>49</v>
@@ -1670,16 +1670,16 @@
         <v>375</v>
       </c>
       <c r="K18" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="L18" s="16" t="s">
         <v>56</v>
-      </c>
-      <c r="L18" s="16" t="s">
-        <v>57</v>
       </c>
       <c r="M18" s="16" t="s">
         <v>49</v>
       </c>
       <c r="N18" s="17" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O18" s="17">
         <v>6632</v>
@@ -1719,16 +1719,16 @@
         <v>345</v>
       </c>
       <c r="K19" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="L19" s="16" t="s">
         <v>56</v>
-      </c>
-      <c r="L19" s="16" t="s">
-        <v>57</v>
       </c>
       <c r="M19" s="16" t="s">
         <v>49</v>
       </c>
       <c r="N19" s="17" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="O19" s="17">
         <v>10243</v>
@@ -1739,25 +1739,25 @@
         <v>46260</v>
       </c>
       <c r="B20" s="14" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C20" s="14" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D20" s="14" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E20" s="14" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F20" s="14" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G20" s="14" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H20" s="14" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I20" s="15" t="str">
         <f t="shared" si="0"/>
@@ -1780,25 +1780,25 @@
         <v>46261</v>
       </c>
       <c r="B21" s="14" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C21" s="14" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D21" s="14" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E21" s="14" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F21" s="14" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G21" s="14" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H21" s="14" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I21" s="15" t="str">
         <f t="shared" si="0"/>
@@ -1821,25 +1821,25 @@
         <v>46262</v>
       </c>
       <c r="B22" s="14" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C22" s="14" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D22" s="14" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E22" s="14" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F22" s="14" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G22" s="14" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H22" s="14" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I22" s="15" t="str">
         <f t="shared" si="0"/>
@@ -1862,25 +1862,25 @@
         <v>46263</v>
       </c>
       <c r="B23" s="14" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C23" s="14" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D23" s="14" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E23" s="14" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F23" s="14" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G23" s="14" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H23" s="14" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I23" s="15" t="str">
         <f t="shared" si="0"/>
@@ -1903,25 +1903,25 @@
         <v>46264</v>
       </c>
       <c r="B24" s="14" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C24" s="14" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D24" s="14" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E24" s="14" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F24" s="14" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G24" s="14" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H24" s="14" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I24" s="15" t="str">
         <f t="shared" si="0"/>
@@ -1973,13 +1973,13 @@
         <v>645</v>
       </c>
       <c r="K25" s="16" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="L25" s="16" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="M25" s="16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="N25" s="17"/>
       <c r="O25" s="17">
@@ -2020,13 +2020,13 @@
         <v>525</v>
       </c>
       <c r="K26" s="16" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="L26" s="16" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="M26" s="16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="N26" s="17"/>
       <c r="O26" s="17">
@@ -2067,10 +2067,10 @@
         <v>615</v>
       </c>
       <c r="K27" s="16" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="L27" s="16" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="M27" s="16" t="s">
         <v>49</v>
@@ -2114,16 +2114,16 @@
         <v>800</v>
       </c>
       <c r="K28" s="16" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="L28" s="16" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="M28" s="16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="N28" s="17" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="O28" s="17">
         <v>788</v>
@@ -2163,16 +2163,16 @@
         <v>640</v>
       </c>
       <c r="K29" s="16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="L29" s="16" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="M29" s="16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="N29" s="17" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="O29" s="17">
         <v>6663</v>
@@ -2293,10 +2293,10 @@
         <v>480</v>
       </c>
       <c r="K33" s="16" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="L33" s="16" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="M33" s="16" t="s">
         <v>49</v>
@@ -2340,16 +2340,16 @@
         <v>520</v>
       </c>
       <c r="K34" s="16" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="L34" s="16" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="M34" s="16" t="s">
         <v>49</v>
       </c>
       <c r="N34" s="17" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="O34" s="17">
         <v>8053</v>
@@ -2389,10 +2389,10 @@
         <v>700</v>
       </c>
       <c r="K35" s="16" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="L35" s="16" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="M35" s="16" t="s">
         <v>49</v>
@@ -2436,30 +2436,46 @@
         <v>380</v>
       </c>
       <c r="K36" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="L36" s="16" t="s">
         <v>56</v>
-      </c>
-      <c r="L36" s="16" t="s">
-        <v>57</v>
       </c>
       <c r="M36" s="16" t="s">
         <v>49</v>
       </c>
       <c r="N36" s="17" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="O36" s="17">
         <v>9271</v>
       </c>
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A37" s="13"/>
-      <c r="B37" s="14"/>
-      <c r="C37" s="14"/>
-      <c r="D37" s="14"/>
-      <c r="E37" s="14"/>
-      <c r="F37" s="14"/>
-      <c r="G37" s="14"/>
-      <c r="H37" s="14"/>
+      <c r="A37" s="8">
+        <v>46277</v>
+      </c>
+      <c r="B37" s="14" t="s">
+        <v>72</v>
+      </c>
+      <c r="C37" s="14" t="s">
+        <v>72</v>
+      </c>
+      <c r="D37" s="14" t="s">
+        <v>72</v>
+      </c>
+      <c r="E37" s="14" t="s">
+        <v>72</v>
+      </c>
+      <c r="F37" s="14" t="s">
+        <v>72</v>
+      </c>
+      <c r="G37" s="14" t="s">
+        <v>72</v>
+      </c>
+      <c r="H37" s="14" t="s">
+        <v>72</v>
+      </c>
       <c r="I37" s="15" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -2472,17 +2488,35 @@
       <c r="L37" s="16"/>
       <c r="M37" s="16"/>
       <c r="N37" s="17"/>
-      <c r="O37" s="17"/>
+      <c r="O37" s="17">
+        <v>562</v>
+      </c>
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A38" s="13"/>
-      <c r="B38" s="14"/>
-      <c r="C38" s="14"/>
-      <c r="D38" s="14"/>
-      <c r="E38" s="14"/>
-      <c r="F38" s="14"/>
-      <c r="G38" s="14"/>
-      <c r="H38" s="14"/>
+      <c r="A38" s="8">
+        <v>46278</v>
+      </c>
+      <c r="B38" s="14" t="s">
+        <v>72</v>
+      </c>
+      <c r="C38" s="14" t="s">
+        <v>72</v>
+      </c>
+      <c r="D38" s="14" t="s">
+        <v>72</v>
+      </c>
+      <c r="E38" s="14" t="s">
+        <v>72</v>
+      </c>
+      <c r="F38" s="14" t="s">
+        <v>72</v>
+      </c>
+      <c r="G38" s="14" t="s">
+        <v>72</v>
+      </c>
+      <c r="H38" s="14" t="s">
+        <v>72</v>
+      </c>
       <c r="I38" s="15" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -2495,10 +2529,14 @@
       <c r="L38" s="16"/>
       <c r="M38" s="16"/>
       <c r="N38" s="17"/>
-      <c r="O38" s="17"/>
+      <c r="O38" s="17">
+        <v>208</v>
+      </c>
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A39" s="13"/>
+      <c r="A39" s="8">
+        <v>46279</v>
+      </c>
       <c r="B39" s="14"/>
       <c r="C39" s="14"/>
       <c r="D39" s="14"/>
@@ -2518,53 +2556,103 @@
       <c r="L39" s="16"/>
       <c r="M39" s="16"/>
       <c r="N39" s="17"/>
-      <c r="O39" s="17"/>
+      <c r="O39" s="17">
+        <v>7204</v>
+      </c>
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A40" s="13"/>
-      <c r="B40" s="14"/>
-      <c r="C40" s="14"/>
-      <c r="D40" s="14"/>
-      <c r="E40" s="14"/>
-      <c r="F40" s="14"/>
-      <c r="G40" s="14"/>
-      <c r="H40" s="14"/>
-      <c r="I40" s="15" t="str">
+      <c r="A40" s="8">
+        <v>46280</v>
+      </c>
+      <c r="B40" s="14">
+        <v>210</v>
+      </c>
+      <c r="C40" s="14">
+        <v>40</v>
+      </c>
+      <c r="D40" s="14">
+        <v>30</v>
+      </c>
+      <c r="E40" s="14">
+        <v>25</v>
+      </c>
+      <c r="F40" s="14">
+        <v>250</v>
+      </c>
+      <c r="G40" s="14">
+        <v>5</v>
+      </c>
+      <c r="H40" s="14">
+        <v>450</v>
+      </c>
+      <c r="I40" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J40" s="15" t="str">
+        <v>1005</v>
+      </c>
+      <c r="J40" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K40" s="16"/>
-      <c r="L40" s="16"/>
-      <c r="M40" s="16"/>
+        <v>435</v>
+      </c>
+      <c r="K40" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="L40" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="M40" s="16" t="s">
+        <v>49</v>
+      </c>
       <c r="N40" s="17"/>
-      <c r="O40" s="17"/>
+      <c r="O40" s="17">
+        <v>6514</v>
+      </c>
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A41" s="13"/>
-      <c r="B41" s="14"/>
-      <c r="C41" s="14"/>
-      <c r="D41" s="14"/>
-      <c r="E41" s="14"/>
-      <c r="F41" s="14"/>
-      <c r="G41" s="14"/>
-      <c r="H41" s="14"/>
-      <c r="I41" s="15" t="str">
+      <c r="A41" s="8">
+        <v>46281</v>
+      </c>
+      <c r="B41" s="14">
+        <v>200</v>
+      </c>
+      <c r="C41" s="14">
+        <v>30</v>
+      </c>
+      <c r="D41" s="14">
+        <v>0</v>
+      </c>
+      <c r="E41" s="14">
+        <v>0</v>
+      </c>
+      <c r="F41" s="14">
+        <v>100</v>
+      </c>
+      <c r="G41" s="14">
+        <v>2</v>
+      </c>
+      <c r="H41" s="14">
+        <v>500</v>
+      </c>
+      <c r="I41" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J41" s="15" t="str">
+        <v>830</v>
+      </c>
+      <c r="J41" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K41" s="16"/>
-      <c r="L41" s="16"/>
-      <c r="M41" s="16"/>
+        <v>610</v>
+      </c>
+      <c r="K41" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="L41" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="M41" s="16" t="s">
+        <v>49</v>
+      </c>
       <c r="N41" s="17"/>
-      <c r="O41" s="17"/>
+      <c r="O41" s="17">
+        <v>7726</v>
+      </c>
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A42" s="13"/>

--- a/12618117.xlsx
+++ b/12618117.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Krish\Desktop\MCA_SEM1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F62067A-D381-4A64-8EA4-968F87CA4BA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D85BFDC-E7E3-4777-8380-86B2169D6D7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="79">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -269,6 +269,9 @@
   </si>
   <si>
     <t>August, September</t>
+  </si>
+  <si>
+    <t>It was nice weather today with cold breeze</t>
   </si>
 </sst>
 </file>
@@ -2654,28 +2657,54 @@
         <v>7726</v>
       </c>
     </row>
-    <row r="42" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A42" s="13"/>
-      <c r="B42" s="14"/>
-      <c r="C42" s="14"/>
-      <c r="D42" s="14"/>
-      <c r="E42" s="14"/>
-      <c r="F42" s="14"/>
-      <c r="G42" s="14"/>
-      <c r="H42" s="14"/>
-      <c r="I42" s="15" t="str">
+    <row r="42" spans="1:15" ht="29" x14ac:dyDescent="0.35">
+      <c r="A42" s="8">
+        <v>46282</v>
+      </c>
+      <c r="B42" s="14">
+        <v>180</v>
+      </c>
+      <c r="C42" s="14">
+        <v>30</v>
+      </c>
+      <c r="D42" s="14">
+        <v>40</v>
+      </c>
+      <c r="E42" s="14">
+        <v>40</v>
+      </c>
+      <c r="F42" s="14">
+        <v>300</v>
+      </c>
+      <c r="G42" s="14">
+        <v>6</v>
+      </c>
+      <c r="H42" s="14">
+        <v>450</v>
+      </c>
+      <c r="I42" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J42" s="15" t="str">
+        <v>1040</v>
+      </c>
+      <c r="J42" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K42" s="16"/>
-      <c r="L42" s="16"/>
-      <c r="M42" s="16"/>
-      <c r="N42" s="17"/>
-      <c r="O42" s="17"/>
+        <v>400</v>
+      </c>
+      <c r="K42" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="L42" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M42" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="N42" s="17" t="s">
+        <v>78</v>
+      </c>
+      <c r="O42" s="17">
+        <v>9034</v>
+      </c>
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A43" s="13"/>

--- a/12618117.xlsx
+++ b/12618117.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Krish\Desktop\MCA_SEM1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D85BFDC-E7E3-4777-8380-86B2169D6D7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0071A8C5-56A3-4E73-AB74-47891E0BA158}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="79">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2707,27 +2707,51 @@
       </c>
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A43" s="13"/>
-      <c r="B43" s="14"/>
-      <c r="C43" s="14"/>
-      <c r="D43" s="14"/>
-      <c r="E43" s="14"/>
-      <c r="F43" s="14"/>
-      <c r="G43" s="14"/>
-      <c r="H43" s="14"/>
-      <c r="I43" s="15" t="str">
+      <c r="A43" s="8">
+        <v>46283</v>
+      </c>
+      <c r="B43" s="14">
+        <v>180</v>
+      </c>
+      <c r="C43" s="14">
+        <v>40</v>
+      </c>
+      <c r="D43" s="14">
+        <v>35</v>
+      </c>
+      <c r="E43" s="14">
+        <v>45</v>
+      </c>
+      <c r="F43" s="14">
+        <v>350</v>
+      </c>
+      <c r="G43" s="14">
+        <v>7</v>
+      </c>
+      <c r="H43" s="14">
+        <v>400</v>
+      </c>
+      <c r="I43" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J43" s="15" t="str">
+        <v>1050</v>
+      </c>
+      <c r="J43" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K43" s="16"/>
-      <c r="L43" s="16"/>
-      <c r="M43" s="16"/>
+        <v>390</v>
+      </c>
+      <c r="K43" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="L43" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="M43" s="16" t="s">
+        <v>49</v>
+      </c>
       <c r="N43" s="17"/>
-      <c r="O43" s="17"/>
+      <c r="O43" s="17">
+        <v>9207</v>
+      </c>
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A44" s="13"/>

--- a/12618117.xlsx
+++ b/12618117.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Krish\Desktop\MCA_SEM1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0071A8C5-56A3-4E73-AB74-47891E0BA158}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{575C60FC-281F-4AA6-BCC3-CCBB025DD12A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="81">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -272,6 +272,12 @@
   </si>
   <si>
     <t>It was nice weather today with cold breeze</t>
+  </si>
+  <si>
+    <t>Today it was CA of Analytical it was eassy one.</t>
+  </si>
+  <si>
+    <t>I did python assignment, washed clothes, applied face mask and worked on ResumeOS</t>
   </si>
 </sst>
 </file>
@@ -2041,7 +2047,7 @@
         <v>46267</v>
       </c>
       <c r="B27" s="14">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="C27" s="14">
         <v>45</v>
@@ -2063,11 +2069,11 @@
       </c>
       <c r="I27" s="15">
         <f t="shared" si="0"/>
-        <v>825</v>
+        <v>1025</v>
       </c>
       <c r="J27" s="15">
         <f t="shared" si="1"/>
-        <v>615</v>
+        <v>415</v>
       </c>
       <c r="K27" s="16" t="s">
         <v>53</v>
@@ -2088,7 +2094,7 @@
         <v>46268</v>
       </c>
       <c r="B28" s="14">
-        <v>200</v>
+        <v>410</v>
       </c>
       <c r="C28" s="14">
         <v>30</v>
@@ -2110,11 +2116,11 @@
       </c>
       <c r="I28" s="15">
         <f t="shared" si="0"/>
-        <v>640</v>
+        <v>850</v>
       </c>
       <c r="J28" s="15">
         <f t="shared" si="1"/>
-        <v>800</v>
+        <v>590</v>
       </c>
       <c r="K28" s="16" t="s">
         <v>53</v>
@@ -2363,7 +2369,7 @@
         <v>46275</v>
       </c>
       <c r="B35" s="14">
-        <v>200</v>
+        <v>290</v>
       </c>
       <c r="C35" s="14">
         <v>30</v>
@@ -2385,11 +2391,11 @@
       </c>
       <c r="I35" s="15">
         <f t="shared" si="0"/>
-        <v>740</v>
+        <v>830</v>
       </c>
       <c r="J35" s="15">
         <f t="shared" si="1"/>
-        <v>700</v>
+        <v>610</v>
       </c>
       <c r="K35" s="16" t="s">
         <v>53</v>
@@ -2568,7 +2574,7 @@
         <v>46280</v>
       </c>
       <c r="B40" s="14">
-        <v>210</v>
+        <v>400</v>
       </c>
       <c r="C40" s="14">
         <v>40</v>
@@ -2590,11 +2596,11 @@
       </c>
       <c r="I40" s="15">
         <f t="shared" si="0"/>
-        <v>1005</v>
+        <v>1195</v>
       </c>
       <c r="J40" s="15">
         <f t="shared" si="1"/>
-        <v>435</v>
+        <v>245</v>
       </c>
       <c r="K40" s="16" t="s">
         <v>53</v>
@@ -2711,7 +2717,7 @@
         <v>46283</v>
       </c>
       <c r="B43" s="14">
-        <v>180</v>
+        <v>350</v>
       </c>
       <c r="C43" s="14">
         <v>40</v>
@@ -2733,11 +2739,11 @@
       </c>
       <c r="I43" s="15">
         <f t="shared" si="0"/>
-        <v>1050</v>
+        <v>1220</v>
       </c>
       <c r="J43" s="15">
         <f t="shared" si="1"/>
-        <v>390</v>
+        <v>220</v>
       </c>
       <c r="K43" s="16" t="s">
         <v>53</v>
@@ -2753,51 +2759,103 @@
         <v>9207</v>
       </c>
     </row>
-    <row r="44" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A44" s="13"/>
-      <c r="B44" s="14"/>
-      <c r="C44" s="14"/>
-      <c r="D44" s="14"/>
-      <c r="E44" s="14"/>
-      <c r="F44" s="14"/>
-      <c r="G44" s="14"/>
-      <c r="H44" s="14"/>
-      <c r="I44" s="15" t="str">
+    <row r="44" spans="1:15" ht="29" x14ac:dyDescent="0.35">
+      <c r="A44" s="8">
+        <v>46284</v>
+      </c>
+      <c r="B44" s="14">
+        <v>200</v>
+      </c>
+      <c r="C44" s="14">
+        <v>35</v>
+      </c>
+      <c r="D44" s="14">
+        <v>40</v>
+      </c>
+      <c r="E44" s="14">
+        <v>0</v>
+      </c>
+      <c r="F44" s="14">
+        <v>70</v>
+      </c>
+      <c r="G44" s="14">
+        <v>1</v>
+      </c>
+      <c r="H44" s="14">
+        <v>500</v>
+      </c>
+      <c r="I44" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J44" s="15" t="str">
+        <v>845</v>
+      </c>
+      <c r="J44" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K44" s="16"/>
-      <c r="L44" s="16"/>
-      <c r="M44" s="16"/>
-      <c r="N44" s="17"/>
-      <c r="O44" s="17"/>
-    </row>
-    <row r="45" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A45" s="13"/>
-      <c r="B45" s="14"/>
-      <c r="C45" s="14"/>
-      <c r="D45" s="14"/>
-      <c r="E45" s="14"/>
-      <c r="F45" s="14"/>
-      <c r="G45" s="14"/>
-      <c r="H45" s="14"/>
-      <c r="I45" s="15" t="str">
+        <v>595</v>
+      </c>
+      <c r="K44" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="L44" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="M44" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="N44" s="17" t="s">
+        <v>79</v>
+      </c>
+      <c r="O44" s="17">
+        <v>5640</v>
+      </c>
+    </row>
+    <row r="45" spans="1:15" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A45" s="8">
+        <v>46285</v>
+      </c>
+      <c r="B45" s="14">
+        <v>305</v>
+      </c>
+      <c r="C45" s="14">
+        <v>20</v>
+      </c>
+      <c r="D45" s="14">
+        <v>200</v>
+      </c>
+      <c r="E45" s="14">
+        <v>30</v>
+      </c>
+      <c r="F45" s="14">
+        <v>0</v>
+      </c>
+      <c r="G45" s="14">
+        <v>0</v>
+      </c>
+      <c r="H45" s="14">
+        <v>400</v>
+      </c>
+      <c r="I45" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J45" s="15" t="str">
+        <v>955</v>
+      </c>
+      <c r="J45" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K45" s="16"/>
-      <c r="L45" s="16"/>
-      <c r="M45" s="16"/>
-      <c r="N45" s="17"/>
-      <c r="O45" s="17"/>
+        <v>485</v>
+      </c>
+      <c r="K45" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="L45" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="M45" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="N45" s="17" t="s">
+        <v>80</v>
+      </c>
+      <c r="O45" s="17">
+        <v>600</v>
+      </c>
     </row>
     <row r="46" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A46" s="13"/>

--- a/12618117.xlsx
+++ b/12618117.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Krish\Desktop\MCA_SEM1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{575C60FC-281F-4AA6-BCC3-CCBB025DD12A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77D35452-30C6-4367-8245-0D0924AFDE0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="18750" windowHeight="10530" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="83">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -278,6 +278,12 @@
   </si>
   <si>
     <t>I did python assignment, washed clothes, applied face mask and worked on ResumeOS</t>
+  </si>
+  <si>
+    <t>40l</t>
+  </si>
+  <si>
+    <t>0l</t>
   </si>
 </sst>
 </file>
@@ -1747,26 +1753,26 @@
       <c r="A20" s="8">
         <v>46260</v>
       </c>
-      <c r="B20" s="14" t="s">
-        <v>72</v>
-      </c>
-      <c r="C20" s="14" t="s">
-        <v>72</v>
-      </c>
-      <c r="D20" s="14" t="s">
-        <v>72</v>
-      </c>
-      <c r="E20" s="14" t="s">
-        <v>72</v>
-      </c>
-      <c r="F20" s="14" t="s">
-        <v>72</v>
-      </c>
-      <c r="G20" s="14" t="s">
-        <v>72</v>
-      </c>
-      <c r="H20" s="14" t="s">
-        <v>72</v>
+      <c r="B20" s="14">
+        <v>0</v>
+      </c>
+      <c r="C20" s="14">
+        <v>0</v>
+      </c>
+      <c r="D20" s="14">
+        <v>0</v>
+      </c>
+      <c r="E20" s="14">
+        <v>0</v>
+      </c>
+      <c r="F20" s="14">
+        <v>0</v>
+      </c>
+      <c r="G20" s="14">
+        <v>0</v>
+      </c>
+      <c r="H20" s="14">
+        <v>0</v>
       </c>
       <c r="I20" s="15" t="str">
         <f t="shared" si="0"/>
@@ -1776,9 +1782,15 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K20" s="16"/>
-      <c r="L20" s="16"/>
-      <c r="M20" s="16"/>
+      <c r="K20" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="L20" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="M20" s="16" t="s">
+        <v>62</v>
+      </c>
       <c r="N20" s="17"/>
       <c r="O20" s="17">
         <v>8649</v>
@@ -1788,38 +1800,44 @@
       <c r="A21" s="8">
         <v>46261</v>
       </c>
-      <c r="B21" s="14" t="s">
-        <v>72</v>
-      </c>
-      <c r="C21" s="14" t="s">
-        <v>72</v>
-      </c>
-      <c r="D21" s="14" t="s">
-        <v>72</v>
-      </c>
-      <c r="E21" s="14" t="s">
-        <v>72</v>
-      </c>
-      <c r="F21" s="14" t="s">
-        <v>72</v>
-      </c>
-      <c r="G21" s="14" t="s">
-        <v>72</v>
-      </c>
-      <c r="H21" s="14" t="s">
-        <v>72</v>
-      </c>
-      <c r="I21" s="15" t="str">
+      <c r="B21" s="14">
+        <v>220</v>
+      </c>
+      <c r="C21" s="14">
+        <v>30</v>
+      </c>
+      <c r="D21" s="14">
+        <v>120</v>
+      </c>
+      <c r="E21" s="14">
+        <v>30</v>
+      </c>
+      <c r="F21" s="14">
+        <v>250</v>
+      </c>
+      <c r="G21" s="14">
+        <v>5</v>
+      </c>
+      <c r="H21" s="14">
+        <v>270</v>
+      </c>
+      <c r="I21" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J21" s="15" t="str">
+        <v>920</v>
+      </c>
+      <c r="J21" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K21" s="16"/>
-      <c r="L21" s="16"/>
-      <c r="M21" s="16"/>
+        <v>520</v>
+      </c>
+      <c r="K21" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="L21" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="M21" s="16" t="s">
+        <v>49</v>
+      </c>
       <c r="N21" s="17"/>
       <c r="O21" s="17">
         <v>3129</v>
@@ -1829,38 +1847,44 @@
       <c r="A22" s="8">
         <v>46262</v>
       </c>
-      <c r="B22" s="14" t="s">
-        <v>72</v>
+      <c r="B22" s="14">
+        <v>200</v>
       </c>
       <c r="C22" s="14" t="s">
-        <v>72</v>
-      </c>
-      <c r="D22" s="14" t="s">
-        <v>72</v>
-      </c>
-      <c r="E22" s="14" t="s">
-        <v>72</v>
-      </c>
-      <c r="F22" s="14" t="s">
-        <v>72</v>
-      </c>
-      <c r="G22" s="14" t="s">
-        <v>72</v>
-      </c>
-      <c r="H22" s="14" t="s">
-        <v>72</v>
-      </c>
-      <c r="I22" s="15" t="str">
+        <v>81</v>
+      </c>
+      <c r="D22" s="14">
+        <v>60</v>
+      </c>
+      <c r="E22" s="14">
+        <v>45</v>
+      </c>
+      <c r="F22" s="14">
+        <v>300</v>
+      </c>
+      <c r="G22" s="14">
+        <v>6</v>
+      </c>
+      <c r="H22" s="14">
+        <v>350</v>
+      </c>
+      <c r="I22" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J22" s="15" t="str">
+        <v>955</v>
+      </c>
+      <c r="J22" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K22" s="16"/>
-      <c r="L22" s="16"/>
-      <c r="M22" s="16"/>
+        <v>485</v>
+      </c>
+      <c r="K22" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="L22" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="M22" s="16" t="s">
+        <v>49</v>
+      </c>
       <c r="N22" s="17"/>
       <c r="O22" s="17">
         <v>3902</v>
@@ -1870,38 +1894,44 @@
       <c r="A23" s="8">
         <v>46263</v>
       </c>
-      <c r="B23" s="14" t="s">
-        <v>72</v>
-      </c>
-      <c r="C23" s="14" t="s">
-        <v>72</v>
-      </c>
-      <c r="D23" s="14" t="s">
-        <v>72</v>
-      </c>
-      <c r="E23" s="14" t="s">
-        <v>72</v>
-      </c>
-      <c r="F23" s="14" t="s">
-        <v>72</v>
-      </c>
-      <c r="G23" s="14" t="s">
-        <v>72</v>
-      </c>
-      <c r="H23" s="14" t="s">
-        <v>72</v>
-      </c>
-      <c r="I23" s="15" t="str">
+      <c r="B23" s="14">
+        <v>300</v>
+      </c>
+      <c r="C23" s="14">
+        <v>0</v>
+      </c>
+      <c r="D23" s="14">
+        <v>150</v>
+      </c>
+      <c r="E23" s="14">
+        <v>50</v>
+      </c>
+      <c r="F23" s="14">
+        <v>0</v>
+      </c>
+      <c r="G23" s="14">
+        <v>0</v>
+      </c>
+      <c r="H23" s="14">
+        <v>300</v>
+      </c>
+      <c r="I23" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J23" s="15" t="str">
+        <v>800</v>
+      </c>
+      <c r="J23" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K23" s="16"/>
-      <c r="L23" s="16"/>
-      <c r="M23" s="16"/>
+        <v>640</v>
+      </c>
+      <c r="K23" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="L23" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="M23" s="16" t="s">
+        <v>49</v>
+      </c>
       <c r="N23" s="17"/>
       <c r="O23" s="17">
         <v>804</v>
@@ -1911,38 +1941,44 @@
       <c r="A24" s="8">
         <v>46264</v>
       </c>
-      <c r="B24" s="14" t="s">
-        <v>72</v>
-      </c>
-      <c r="C24" s="14" t="s">
-        <v>72</v>
-      </c>
-      <c r="D24" s="14" t="s">
-        <v>72</v>
-      </c>
-      <c r="E24" s="14" t="s">
-        <v>72</v>
-      </c>
-      <c r="F24" s="14" t="s">
-        <v>72</v>
+      <c r="B24" s="14">
+        <v>400</v>
+      </c>
+      <c r="C24" s="14">
+        <v>0</v>
+      </c>
+      <c r="D24" s="14">
+        <v>0</v>
+      </c>
+      <c r="E24" s="14">
+        <v>70</v>
+      </c>
+      <c r="F24" s="14">
+        <v>0</v>
       </c>
       <c r="G24" s="14" t="s">
-        <v>72</v>
-      </c>
-      <c r="H24" s="14" t="s">
-        <v>72</v>
-      </c>
-      <c r="I24" s="15" t="str">
+        <v>82</v>
+      </c>
+      <c r="H24" s="14">
+        <v>430</v>
+      </c>
+      <c r="I24" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J24" s="15" t="str">
+        <v>900</v>
+      </c>
+      <c r="J24" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K24" s="16"/>
-      <c r="L24" s="16"/>
-      <c r="M24" s="16"/>
+        <v>540</v>
+      </c>
+      <c r="K24" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="L24" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="M24" s="16" t="s">
+        <v>49</v>
+      </c>
       <c r="N24" s="17"/>
       <c r="O24" s="17">
         <v>3091</v>
@@ -2191,24 +2227,44 @@
       <c r="A30" s="8">
         <v>46270</v>
       </c>
-      <c r="B30" s="14"/>
-      <c r="C30" s="14"/>
-      <c r="D30" s="14"/>
-      <c r="E30" s="14"/>
-      <c r="F30" s="14"/>
-      <c r="G30" s="14"/>
-      <c r="H30" s="14"/>
-      <c r="I30" s="15" t="str">
+      <c r="B30" s="14">
+        <v>310</v>
+      </c>
+      <c r="C30" s="14">
+        <v>40</v>
+      </c>
+      <c r="D30" s="14">
+        <v>130</v>
+      </c>
+      <c r="E30" s="14">
+        <v>70</v>
+      </c>
+      <c r="F30" s="14">
+        <v>0</v>
+      </c>
+      <c r="G30" s="14">
+        <v>0</v>
+      </c>
+      <c r="H30" s="14">
+        <v>500</v>
+      </c>
+      <c r="I30" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J30" s="15" t="str">
+        <v>1050</v>
+      </c>
+      <c r="J30" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K30" s="16"/>
-      <c r="L30" s="16"/>
-      <c r="M30" s="16"/>
+        <v>390</v>
+      </c>
+      <c r="K30" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="L30" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="M30" s="16" t="s">
+        <v>49</v>
+      </c>
       <c r="N30" s="17"/>
       <c r="O30" s="17">
         <v>284</v>
@@ -2218,24 +2274,44 @@
       <c r="A31" s="8">
         <v>46271</v>
       </c>
-      <c r="B31" s="14"/>
-      <c r="C31" s="14"/>
-      <c r="D31" s="14"/>
-      <c r="E31" s="14"/>
-      <c r="F31" s="14"/>
-      <c r="G31" s="14"/>
-      <c r="H31" s="14"/>
-      <c r="I31" s="15" t="str">
+      <c r="B31" s="14">
+        <v>350</v>
+      </c>
+      <c r="C31" s="14">
+        <v>0</v>
+      </c>
+      <c r="D31" s="14">
+        <v>0</v>
+      </c>
+      <c r="E31" s="14">
+        <v>0</v>
+      </c>
+      <c r="F31" s="14">
+        <v>0</v>
+      </c>
+      <c r="G31" s="14">
+        <v>0</v>
+      </c>
+      <c r="H31" s="14">
+        <v>700</v>
+      </c>
+      <c r="I31" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J31" s="15" t="str">
+        <v>1050</v>
+      </c>
+      <c r="J31" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K31" s="16"/>
-      <c r="L31" s="16"/>
-      <c r="M31" s="16"/>
+        <v>390</v>
+      </c>
+      <c r="K31" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="L31" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="M31" s="16" t="s">
+        <v>49</v>
+      </c>
       <c r="N31" s="17"/>
       <c r="O31" s="17">
         <v>815</v>
@@ -2245,24 +2321,44 @@
       <c r="A32" s="8">
         <v>46272</v>
       </c>
-      <c r="B32" s="14"/>
-      <c r="C32" s="14"/>
-      <c r="D32" s="14"/>
-      <c r="E32" s="14"/>
-      <c r="F32" s="14"/>
-      <c r="G32" s="14"/>
-      <c r="H32" s="14"/>
-      <c r="I32" s="15" t="str">
+      <c r="B32" s="14">
+        <v>220</v>
+      </c>
+      <c r="C32" s="14">
+        <v>45</v>
+      </c>
+      <c r="D32" s="14">
+        <v>100</v>
+      </c>
+      <c r="E32" s="14">
+        <v>40</v>
+      </c>
+      <c r="F32" s="14">
+        <v>200</v>
+      </c>
+      <c r="G32" s="14">
+        <v>4</v>
+      </c>
+      <c r="H32" s="14">
+        <v>450</v>
+      </c>
+      <c r="I32" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J32" s="15" t="str">
+        <v>1055</v>
+      </c>
+      <c r="J32" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K32" s="16"/>
-      <c r="L32" s="16"/>
-      <c r="M32" s="16"/>
+        <v>385</v>
+      </c>
+      <c r="K32" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="L32" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="M32" s="16" t="s">
+        <v>49</v>
+      </c>
       <c r="N32" s="17"/>
       <c r="O32" s="17">
         <v>10166</v>
@@ -2479,11 +2575,11 @@
       <c r="F37" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="G37" s="14" t="s">
-        <v>72</v>
-      </c>
-      <c r="H37" s="14" t="s">
-        <v>72</v>
+      <c r="G37" s="14">
+        <v>0</v>
+      </c>
+      <c r="H37" s="14">
+        <v>0</v>
       </c>
       <c r="I37" s="15" t="str">
         <f t="shared" si="0"/>
@@ -2493,9 +2589,15 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K37" s="16"/>
-      <c r="L37" s="16"/>
-      <c r="M37" s="16"/>
+      <c r="K37" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="L37" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="M37" s="16" t="s">
+        <v>49</v>
+      </c>
       <c r="N37" s="17"/>
       <c r="O37" s="17">
         <v>562</v>
@@ -2520,11 +2622,9 @@
       <c r="F38" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="G38" s="14" t="s">
-        <v>72</v>
-      </c>
-      <c r="H38" s="14" t="s">
-        <v>72</v>
+      <c r="G38" s="14"/>
+      <c r="H38" s="14">
+        <v>0</v>
       </c>
       <c r="I38" s="15" t="str">
         <f t="shared" si="0"/>
@@ -2534,9 +2634,15 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K38" s="16"/>
-      <c r="L38" s="16"/>
-      <c r="M38" s="16"/>
+      <c r="K38" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="L38" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="M38" s="16" t="s">
+        <v>62</v>
+      </c>
       <c r="N38" s="17"/>
       <c r="O38" s="17">
         <v>208</v>
@@ -2546,24 +2652,44 @@
       <c r="A39" s="8">
         <v>46279</v>
       </c>
-      <c r="B39" s="14"/>
-      <c r="C39" s="14"/>
-      <c r="D39" s="14"/>
-      <c r="E39" s="14"/>
-      <c r="F39" s="14"/>
-      <c r="G39" s="14"/>
-      <c r="H39" s="14"/>
-      <c r="I39" s="15" t="str">
+      <c r="B39" s="14">
+        <v>300</v>
+      </c>
+      <c r="C39" s="14">
+        <v>0</v>
+      </c>
+      <c r="D39" s="14">
+        <v>250</v>
+      </c>
+      <c r="E39" s="14">
+        <v>140</v>
+      </c>
+      <c r="F39" s="14">
+        <v>0</v>
+      </c>
+      <c r="G39" s="14">
+        <v>0</v>
+      </c>
+      <c r="H39" s="14">
+        <v>500</v>
+      </c>
+      <c r="I39" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J39" s="15" t="str">
+        <v>1190</v>
+      </c>
+      <c r="J39" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K39" s="16"/>
-      <c r="L39" s="16"/>
-      <c r="M39" s="16"/>
+        <v>250</v>
+      </c>
+      <c r="K39" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="L39" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="M39" s="16" t="s">
+        <v>49</v>
+      </c>
       <c r="N39" s="17"/>
       <c r="O39" s="17">
         <v>7204</v>
@@ -2858,27 +2984,51 @@
       </c>
     </row>
     <row r="46" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A46" s="13"/>
-      <c r="B46" s="14"/>
-      <c r="C46" s="14"/>
-      <c r="D46" s="14"/>
-      <c r="E46" s="14"/>
-      <c r="F46" s="14"/>
-      <c r="G46" s="14"/>
-      <c r="H46" s="14"/>
-      <c r="I46" s="15" t="str">
+      <c r="A46" s="8">
+        <v>46286</v>
+      </c>
+      <c r="B46" s="14">
+        <v>300</v>
+      </c>
+      <c r="C46" s="14">
+        <v>0</v>
+      </c>
+      <c r="D46" s="14">
+        <v>500</v>
+      </c>
+      <c r="E46" s="14">
+        <v>350</v>
+      </c>
+      <c r="F46" s="14">
+        <v>0</v>
+      </c>
+      <c r="G46" s="14">
+        <v>0</v>
+      </c>
+      <c r="H46" s="14">
+        <v>200</v>
+      </c>
+      <c r="I46" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J46" s="15" t="str">
+        <v>1350</v>
+      </c>
+      <c r="J46" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K46" s="16"/>
-      <c r="L46" s="16"/>
-      <c r="M46" s="16"/>
+        <v>90</v>
+      </c>
+      <c r="K46" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="L46" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M46" s="16" t="s">
+        <v>49</v>
+      </c>
       <c r="N46" s="17"/>
-      <c r="O46" s="17"/>
+      <c r="O46" s="17">
+        <v>450</v>
+      </c>
     </row>
     <row r="47" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A47" s="13"/>

--- a/12618117.xlsx
+++ b/12618117.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Krish\Desktop\MCA_SEM1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77D35452-30C6-4367-8245-0D0924AFDE0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{679EDDDA-1C98-40DD-88AA-3F9BEBD86E21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="18750" windowHeight="10530" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="83">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -268,9 +268,6 @@
     <t>Worked on project ResumeOS</t>
   </si>
   <si>
-    <t>August, September</t>
-  </si>
-  <si>
     <t>It was nice weather today with cold breeze</t>
   </si>
   <si>
@@ -284,6 +281,9 @@
   </si>
   <si>
     <t>0l</t>
+  </si>
+  <si>
+    <t>August, September, October</t>
   </si>
 </sst>
 </file>
@@ -1000,7 +1000,7 @@
         <v>33</v>
       </c>
       <c r="F3" s="21" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="G3" s="21"/>
     </row>
@@ -1851,7 +1851,7 @@
         <v>200</v>
       </c>
       <c r="C22" s="14" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D22" s="14">
         <v>60</v>
@@ -1957,7 +1957,7 @@
         <v>0</v>
       </c>
       <c r="G24" s="14" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H24" s="14">
         <v>430</v>
@@ -2832,7 +2832,7 @@
         <v>49</v>
       </c>
       <c r="N42" s="17" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="O42" s="17">
         <v>9034</v>
@@ -2928,7 +2928,7 @@
         <v>49</v>
       </c>
       <c r="N44" s="17" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="O44" s="17">
         <v>5640</v>
@@ -2977,7 +2977,7 @@
         <v>49</v>
       </c>
       <c r="N45" s="17" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="O45" s="17">
         <v>600</v>
@@ -3031,7 +3031,9 @@
       </c>
     </row>
     <row r="47" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A47" s="13"/>
+      <c r="A47" s="8">
+        <v>46287</v>
+      </c>
       <c r="B47" s="14"/>
       <c r="C47" s="14"/>
       <c r="D47" s="14"/>
@@ -3054,7 +3056,9 @@
       <c r="O47" s="17"/>
     </row>
     <row r="48" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A48" s="13"/>
+      <c r="A48" s="8">
+        <v>46288</v>
+      </c>
       <c r="B48" s="14"/>
       <c r="C48" s="14"/>
       <c r="D48" s="14"/>
@@ -3077,7 +3081,9 @@
       <c r="O48" s="17"/>
     </row>
     <row r="49" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A49" s="13"/>
+      <c r="A49" s="8">
+        <v>46289</v>
+      </c>
       <c r="B49" s="14"/>
       <c r="C49" s="14"/>
       <c r="D49" s="14"/>
@@ -3100,7 +3106,9 @@
       <c r="O49" s="17"/>
     </row>
     <row r="50" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A50" s="13"/>
+      <c r="A50" s="8">
+        <v>46290</v>
+      </c>
       <c r="B50" s="14"/>
       <c r="C50" s="14"/>
       <c r="D50" s="14"/>
@@ -3123,163 +3131,305 @@
       <c r="O50" s="17"/>
     </row>
     <row r="51" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A51" s="13"/>
-      <c r="B51" s="14"/>
-      <c r="C51" s="14"/>
-      <c r="D51" s="14"/>
-      <c r="E51" s="14"/>
-      <c r="F51" s="14"/>
-      <c r="G51" s="14"/>
-      <c r="H51" s="14"/>
-      <c r="I51" s="15" t="str">
+      <c r="A51" s="8">
+        <v>46291</v>
+      </c>
+      <c r="B51" s="14">
+        <v>300</v>
+      </c>
+      <c r="C51" s="14">
+        <v>0</v>
+      </c>
+      <c r="D51" s="14">
+        <v>250</v>
+      </c>
+      <c r="E51" s="14">
+        <v>30</v>
+      </c>
+      <c r="F51" s="14">
+        <v>0</v>
+      </c>
+      <c r="G51" s="14">
+        <v>0</v>
+      </c>
+      <c r="H51" s="14">
+        <v>350</v>
+      </c>
+      <c r="I51" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J51" s="15" t="str">
+        <v>930</v>
+      </c>
+      <c r="J51" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K51" s="16"/>
-      <c r="L51" s="16"/>
-      <c r="M51" s="16"/>
+        <v>510</v>
+      </c>
+      <c r="K51" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="L51" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="M51" s="16" t="s">
+        <v>49</v>
+      </c>
       <c r="N51" s="17"/>
       <c r="O51" s="17"/>
     </row>
     <row r="52" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A52" s="13"/>
+      <c r="A52" s="8">
+        <v>46292</v>
+      </c>
       <c r="B52" s="14"/>
-      <c r="C52" s="14"/>
-      <c r="D52" s="14"/>
-      <c r="E52" s="14"/>
-      <c r="F52" s="14"/>
-      <c r="G52" s="14"/>
-      <c r="H52" s="14"/>
-      <c r="I52" s="15" t="str">
+      <c r="C52" s="14">
+        <v>5</v>
+      </c>
+      <c r="D52" s="14">
+        <v>0</v>
+      </c>
+      <c r="E52" s="14">
+        <v>0</v>
+      </c>
+      <c r="F52" s="14">
+        <v>0</v>
+      </c>
+      <c r="G52" s="14">
+        <v>0</v>
+      </c>
+      <c r="H52" s="14">
+        <v>350</v>
+      </c>
+      <c r="I52" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J52" s="15" t="str">
+        <v>355</v>
+      </c>
+      <c r="J52" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K52" s="16"/>
-      <c r="L52" s="16"/>
-      <c r="M52" s="16"/>
+        <v>1085</v>
+      </c>
+      <c r="K52" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="L52" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="M52" s="16" t="s">
+        <v>49</v>
+      </c>
       <c r="N52" s="17"/>
       <c r="O52" s="17"/>
     </row>
     <row r="53" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A53" s="13"/>
+      <c r="A53" s="8">
+        <v>46293</v>
+      </c>
       <c r="B53" s="14"/>
-      <c r="C53" s="14"/>
-      <c r="D53" s="14"/>
-      <c r="E53" s="14"/>
-      <c r="F53" s="14"/>
-      <c r="G53" s="14"/>
-      <c r="H53" s="14"/>
-      <c r="I53" s="15" t="str">
+      <c r="C53" s="14">
+        <v>10</v>
+      </c>
+      <c r="D53" s="14">
+        <v>30</v>
+      </c>
+      <c r="E53" s="14">
+        <v>0</v>
+      </c>
+      <c r="F53" s="14">
+        <v>0</v>
+      </c>
+      <c r="G53" s="14">
+        <v>0</v>
+      </c>
+      <c r="H53" s="14">
+        <v>400</v>
+      </c>
+      <c r="I53" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J53" s="15" t="str">
+        <v>440</v>
+      </c>
+      <c r="J53" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K53" s="16"/>
-      <c r="L53" s="16"/>
-      <c r="M53" s="16"/>
+        <v>1000</v>
+      </c>
+      <c r="K53" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="L53" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="M53" s="16" t="s">
+        <v>49</v>
+      </c>
       <c r="N53" s="17"/>
       <c r="O53" s="17"/>
     </row>
     <row r="54" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A54" s="13"/>
+      <c r="A54" s="8">
+        <v>46294</v>
+      </c>
       <c r="B54" s="14"/>
-      <c r="C54" s="14"/>
-      <c r="D54" s="14"/>
-      <c r="E54" s="14"/>
-      <c r="F54" s="14"/>
-      <c r="G54" s="14"/>
-      <c r="H54" s="14"/>
-      <c r="I54" s="15" t="str">
+      <c r="C54" s="14">
+        <v>0</v>
+      </c>
+      <c r="D54" s="14">
+        <v>0</v>
+      </c>
+      <c r="E54" s="14">
+        <v>0</v>
+      </c>
+      <c r="F54" s="14">
+        <v>0</v>
+      </c>
+      <c r="G54" s="14">
+        <v>0</v>
+      </c>
+      <c r="H54" s="14">
+        <v>270</v>
+      </c>
+      <c r="I54" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J54" s="15" t="str">
+        <v>270</v>
+      </c>
+      <c r="J54" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K54" s="16"/>
-      <c r="L54" s="16"/>
-      <c r="M54" s="16"/>
+        <v>1170</v>
+      </c>
+      <c r="K54" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="L54" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="M54" s="16" t="s">
+        <v>49</v>
+      </c>
       <c r="N54" s="17"/>
       <c r="O54" s="17"/>
     </row>
     <row r="55" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A55" s="13"/>
+      <c r="A55" s="8">
+        <v>46295</v>
+      </c>
       <c r="B55" s="14"/>
-      <c r="C55" s="14"/>
-      <c r="D55" s="14"/>
-      <c r="E55" s="14"/>
-      <c r="F55" s="14"/>
-      <c r="G55" s="14"/>
-      <c r="H55" s="14"/>
-      <c r="I55" s="15" t="str">
+      <c r="C55" s="14">
+        <v>10</v>
+      </c>
+      <c r="D55" s="14">
+        <v>200</v>
+      </c>
+      <c r="E55" s="14">
+        <v>45</v>
+      </c>
+      <c r="F55" s="14">
+        <v>0</v>
+      </c>
+      <c r="G55" s="14">
+        <v>0</v>
+      </c>
+      <c r="H55" s="14">
+        <v>350</v>
+      </c>
+      <c r="I55" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J55" s="15" t="str">
+        <v>605</v>
+      </c>
+      <c r="J55" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K55" s="16"/>
-      <c r="L55" s="16"/>
-      <c r="M55" s="16"/>
+        <v>835</v>
+      </c>
+      <c r="K55" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="L55" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="M55" s="16" t="s">
+        <v>49</v>
+      </c>
       <c r="N55" s="17"/>
       <c r="O55" s="17"/>
     </row>
     <row r="56" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A56" s="13"/>
+      <c r="A56" s="8">
+        <v>46296</v>
+      </c>
       <c r="B56" s="14"/>
-      <c r="C56" s="14"/>
-      <c r="D56" s="14"/>
-      <c r="E56" s="14"/>
-      <c r="F56" s="14"/>
-      <c r="G56" s="14"/>
-      <c r="H56" s="14"/>
-      <c r="I56" s="15" t="str">
+      <c r="C56" s="14">
+        <v>10</v>
+      </c>
+      <c r="D56" s="14">
+        <v>167</v>
+      </c>
+      <c r="E56" s="14">
+        <v>50</v>
+      </c>
+      <c r="F56" s="14">
+        <v>0</v>
+      </c>
+      <c r="G56" s="14">
+        <v>0</v>
+      </c>
+      <c r="H56" s="14">
+        <v>180</v>
+      </c>
+      <c r="I56" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J56" s="15" t="str">
+        <v>407</v>
+      </c>
+      <c r="J56" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K56" s="16"/>
-      <c r="L56" s="16"/>
-      <c r="M56" s="16"/>
+        <v>1033</v>
+      </c>
+      <c r="K56" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="L56" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M56" s="16" t="s">
+        <v>49</v>
+      </c>
       <c r="N56" s="17"/>
       <c r="O56" s="17"/>
     </row>
     <row r="57" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A57" s="13"/>
+      <c r="A57" s="8">
+        <v>46297</v>
+      </c>
       <c r="B57" s="14"/>
-      <c r="C57" s="14"/>
-      <c r="D57" s="14"/>
-      <c r="E57" s="14"/>
-      <c r="F57" s="14"/>
-      <c r="G57" s="14"/>
-      <c r="H57" s="14"/>
-      <c r="I57" s="15" t="str">
+      <c r="C57" s="14">
+        <v>10</v>
+      </c>
+      <c r="D57" s="14">
+        <v>240</v>
+      </c>
+      <c r="E57" s="14">
+        <v>45</v>
+      </c>
+      <c r="F57" s="14">
+        <v>0</v>
+      </c>
+      <c r="G57" s="14">
+        <v>0</v>
+      </c>
+      <c r="H57" s="14">
+        <v>150</v>
+      </c>
+      <c r="I57" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J57" s="15" t="str">
+        <v>445</v>
+      </c>
+      <c r="J57" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K57" s="16"/>
-      <c r="L57" s="16"/>
-      <c r="M57" s="16"/>
+        <v>995</v>
+      </c>
+      <c r="K57" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="L57" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M57" s="16" t="s">
+        <v>49</v>
+      </c>
       <c r="N57" s="17"/>
       <c r="O57" s="17"/>
     </row>

--- a/12618117.xlsx
+++ b/12618117.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Krish\Desktop\MCA_SEM1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{679EDDDA-1C98-40DD-88AA-3F9BEBD86E21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFFB6A01-09CD-44C5-827A-08CC07DEBC24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="18750" windowHeight="10530" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="84">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -285,6 +285,9 @@
   <si>
     <t>August, September, October</t>
   </si>
+  <si>
+    <t>Came back home</t>
+  </si>
 </sst>
 </file>
 
@@ -473,7 +476,43 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="4">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+        <name val="Arial"/>
+        <charset val="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+        <name val="Arial"/>
+        <charset val="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+        <name val="Arial"/>
+        <charset val="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -3179,7 +3218,9 @@
       <c r="A52" s="8">
         <v>46292</v>
       </c>
-      <c r="B52" s="14"/>
+      <c r="B52" s="14">
+        <v>310</v>
+      </c>
       <c r="C52" s="14">
         <v>5</v>
       </c>
@@ -3200,11 +3241,11 @@
       </c>
       <c r="I52" s="15">
         <f t="shared" si="0"/>
-        <v>355</v>
+        <v>665</v>
       </c>
       <c r="J52" s="15">
         <f t="shared" si="1"/>
-        <v>1085</v>
+        <v>775</v>
       </c>
       <c r="K52" s="16" t="s">
         <v>53</v>
@@ -3222,7 +3263,9 @@
       <c r="A53" s="8">
         <v>46293</v>
       </c>
-      <c r="B53" s="14"/>
+      <c r="B53" s="14">
+        <v>280</v>
+      </c>
       <c r="C53" s="14">
         <v>10</v>
       </c>
@@ -3243,11 +3286,11 @@
       </c>
       <c r="I53" s="15">
         <f t="shared" si="0"/>
-        <v>440</v>
+        <v>720</v>
       </c>
       <c r="J53" s="15">
         <f t="shared" si="1"/>
-        <v>1000</v>
+        <v>720</v>
       </c>
       <c r="K53" s="16" t="s">
         <v>53</v>
@@ -3265,7 +3308,9 @@
       <c r="A54" s="8">
         <v>46294</v>
       </c>
-      <c r="B54" s="14"/>
+      <c r="B54" s="14">
+        <v>300</v>
+      </c>
       <c r="C54" s="14">
         <v>0</v>
       </c>
@@ -3286,11 +3331,11 @@
       </c>
       <c r="I54" s="15">
         <f t="shared" si="0"/>
-        <v>270</v>
+        <v>570</v>
       </c>
       <c r="J54" s="15">
         <f t="shared" si="1"/>
-        <v>1170</v>
+        <v>870</v>
       </c>
       <c r="K54" s="16" t="s">
         <v>53</v>
@@ -3308,7 +3353,9 @@
       <c r="A55" s="8">
         <v>46295</v>
       </c>
-      <c r="B55" s="14"/>
+      <c r="B55" s="14">
+        <v>280</v>
+      </c>
       <c r="C55" s="14">
         <v>10</v>
       </c>
@@ -3329,11 +3376,11 @@
       </c>
       <c r="I55" s="15">
         <f t="shared" si="0"/>
-        <v>605</v>
+        <v>885</v>
       </c>
       <c r="J55" s="15">
         <f t="shared" si="1"/>
-        <v>835</v>
+        <v>555</v>
       </c>
       <c r="K55" s="16" t="s">
         <v>53</v>
@@ -3351,7 +3398,9 @@
       <c r="A56" s="8">
         <v>46296</v>
       </c>
-      <c r="B56" s="14"/>
+      <c r="B56" s="14">
+        <v>260</v>
+      </c>
       <c r="C56" s="14">
         <v>10</v>
       </c>
@@ -3372,11 +3421,11 @@
       </c>
       <c r="I56" s="15">
         <f t="shared" si="0"/>
-        <v>407</v>
+        <v>667</v>
       </c>
       <c r="J56" s="15">
         <f t="shared" si="1"/>
-        <v>1033</v>
+        <v>773</v>
       </c>
       <c r="K56" s="16" t="s">
         <v>55</v>
@@ -3394,7 +3443,9 @@
       <c r="A57" s="8">
         <v>46297</v>
       </c>
-      <c r="B57" s="14"/>
+      <c r="B57" s="14">
+        <v>200</v>
+      </c>
       <c r="C57" s="14">
         <v>10</v>
       </c>
@@ -3415,11 +3466,11 @@
       </c>
       <c r="I57" s="15">
         <f t="shared" si="0"/>
-        <v>445</v>
+        <v>645</v>
       </c>
       <c r="J57" s="15">
         <f t="shared" si="1"/>
-        <v>995</v>
+        <v>795</v>
       </c>
       <c r="K57" s="16" t="s">
         <v>55</v>
@@ -3434,96 +3485,194 @@
       <c r="O57" s="17"/>
     </row>
     <row r="58" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A58" s="13"/>
-      <c r="B58" s="14"/>
-      <c r="C58" s="14"/>
-      <c r="D58" s="14"/>
-      <c r="E58" s="14"/>
-      <c r="F58" s="14"/>
-      <c r="G58" s="14"/>
-      <c r="H58" s="14"/>
-      <c r="I58" s="15" t="str">
+      <c r="A58" s="8">
+        <v>46298</v>
+      </c>
+      <c r="B58" s="14">
+        <v>170</v>
+      </c>
+      <c r="C58" s="14">
+        <v>20</v>
+      </c>
+      <c r="D58" s="14">
+        <v>40</v>
+      </c>
+      <c r="E58" s="14">
+        <v>0</v>
+      </c>
+      <c r="F58" s="14">
+        <v>0</v>
+      </c>
+      <c r="G58" s="14">
+        <v>0</v>
+      </c>
+      <c r="H58" s="14">
+        <v>300</v>
+      </c>
+      <c r="I58" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J58" s="15" t="str">
+        <v>530</v>
+      </c>
+      <c r="J58" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K58" s="16"/>
-      <c r="L58" s="16"/>
-      <c r="M58" s="16"/>
-      <c r="N58" s="17"/>
-      <c r="O58" s="17"/>
+        <v>910</v>
+      </c>
+      <c r="K58" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="L58" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M58" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="N58" s="17" t="s">
+        <v>83</v>
+      </c>
+      <c r="O58" s="17">
+        <v>2737</v>
+      </c>
     </row>
     <row r="59" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A59" s="13"/>
-      <c r="B59" s="14"/>
-      <c r="C59" s="14"/>
-      <c r="D59" s="14"/>
-      <c r="E59" s="14"/>
-      <c r="F59" s="14"/>
-      <c r="G59" s="14"/>
-      <c r="H59" s="14"/>
-      <c r="I59" s="15" t="str">
+      <c r="A59" s="8">
+        <v>46299</v>
+      </c>
+      <c r="B59" s="14">
+        <v>190</v>
+      </c>
+      <c r="C59" s="14">
+        <v>15</v>
+      </c>
+      <c r="D59" s="14">
+        <v>50</v>
+      </c>
+      <c r="E59" s="14">
+        <v>0</v>
+      </c>
+      <c r="F59" s="14">
+        <v>0</v>
+      </c>
+      <c r="G59" s="14">
+        <v>0</v>
+      </c>
+      <c r="H59" s="14">
+        <v>400</v>
+      </c>
+      <c r="I59" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J59" s="15" t="str">
+        <v>655</v>
+      </c>
+      <c r="J59" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K59" s="16"/>
-      <c r="L59" s="16"/>
-      <c r="M59" s="16"/>
+        <v>785</v>
+      </c>
+      <c r="K59" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="L59" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="M59" s="16" t="s">
+        <v>49</v>
+      </c>
       <c r="N59" s="17"/>
-      <c r="O59" s="17"/>
+      <c r="O59" s="17">
+        <v>746</v>
+      </c>
     </row>
     <row r="60" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A60" s="13"/>
-      <c r="B60" s="14"/>
-      <c r="C60" s="14"/>
-      <c r="D60" s="14"/>
-      <c r="E60" s="14"/>
-      <c r="F60" s="14"/>
-      <c r="G60" s="14"/>
-      <c r="H60" s="14"/>
-      <c r="I60" s="15" t="str">
+      <c r="A60" s="8">
+        <v>46300</v>
+      </c>
+      <c r="B60" s="14">
+        <v>170</v>
+      </c>
+      <c r="C60" s="14">
+        <v>10</v>
+      </c>
+      <c r="D60" s="14">
+        <v>40</v>
+      </c>
+      <c r="E60" s="14">
+        <v>0</v>
+      </c>
+      <c r="F60" s="14">
+        <v>200</v>
+      </c>
+      <c r="G60" s="14">
+        <v>4</v>
+      </c>
+      <c r="H60" s="14">
+        <v>340</v>
+      </c>
+      <c r="I60" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J60" s="15" t="str">
+        <v>760</v>
+      </c>
+      <c r="J60" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K60" s="16"/>
-      <c r="L60" s="16"/>
-      <c r="M60" s="16"/>
+        <v>680</v>
+      </c>
+      <c r="K60" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="L60" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="M60" s="16" t="s">
+        <v>49</v>
+      </c>
       <c r="N60" s="17"/>
-      <c r="O60" s="17"/>
+      <c r="O60" s="17">
+        <v>1477</v>
+      </c>
     </row>
     <row r="61" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A61" s="13"/>
-      <c r="B61" s="14"/>
-      <c r="C61" s="14"/>
-      <c r="D61" s="14"/>
-      <c r="E61" s="14"/>
-      <c r="F61" s="14"/>
-      <c r="G61" s="14"/>
-      <c r="H61" s="14"/>
-      <c r="I61" s="15" t="str">
+      <c r="A61" s="8">
+        <v>46301</v>
+      </c>
+      <c r="B61" s="14">
+        <v>180</v>
+      </c>
+      <c r="C61" s="14">
+        <v>15</v>
+      </c>
+      <c r="D61" s="14">
+        <v>40</v>
+      </c>
+      <c r="E61" s="14">
+        <v>0</v>
+      </c>
+      <c r="F61" s="14">
+        <v>250</v>
+      </c>
+      <c r="G61" s="14">
+        <v>5</v>
+      </c>
+      <c r="H61" s="14">
+        <v>240</v>
+      </c>
+      <c r="I61" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J61" s="15" t="str">
+        <v>725</v>
+      </c>
+      <c r="J61" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K61" s="16"/>
-      <c r="L61" s="16"/>
-      <c r="M61" s="16"/>
+        <v>715</v>
+      </c>
+      <c r="K61" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="L61" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="M61" s="16" t="s">
+        <v>49</v>
+      </c>
       <c r="N61" s="17"/>
-      <c r="O61" s="17"/>
+      <c r="O61" s="17">
+        <v>889</v>
+      </c>
     </row>
     <row r="62" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A62" s="13"/>
@@ -11354,8 +11503,18 @@
     <mergeCell ref="B3:D3"/>
     <mergeCell ref="F3:G3"/>
   </mergeCells>
-  <conditionalFormatting sqref="J6:J401">
-    <cfRule type="cellIs" dxfId="0" priority="2" operator="lessThan">
+  <conditionalFormatting sqref="J6:J57 J62:J401">
+    <cfRule type="cellIs" dxfId="3" priority="4" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J58">
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J59:J61">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
